--- a/output/pdf_financials_xlsx/CVB.xlsx
+++ b/output/pdf_financials_xlsx/CVB.xlsx
@@ -6115,52 +6115,52 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.142456</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.221343</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.904791</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.953146</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.953146</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.953146</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.953146</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.687008</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.067986</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.477603</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.693038</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.973874</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>3.154286</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.06689199999999999</v>
+        <v>3.238666</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0.090223</v>
+        <v>2.654042</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0.090223</v>
+        <v>3.306745</v>
       </c>
     </row>
     <row r="93">
@@ -7799,10 +7799,10 @@
         </is>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0</v>
+        <v>-0.030438</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-3.621483</v>
       </c>
       <c r="L118" s="1" t="inlineStr">
         <is>
@@ -7815,19 +7815,19 @@
         </is>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-4.273393</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-1.276441</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.964516</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.525934</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.795079</v>
       </c>
     </row>
     <row r="119">
@@ -10303,7 +10303,11 @@
           <t>Share‐based payment reserve 10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -12267,7 +12271,11 @@
           <t>Share‐based payment reserve 9</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13388,7 +13396,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -14093,7 +14105,11 @@
           <t>Share-based payment reserve 10</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -14982,7 +14998,11 @@
           <t>Share-based payment reserve 7</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -15388,7 +15408,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -15691,7 +15715,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -16297,7 +16325,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -18333,7 +18365,11 @@
           <t>Reserves 11 1,221,343</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -19489,7 +19525,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -20592,7 +20632,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -21695,7 +21739,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
@@ -24319,7 +24367,11 @@
           <t>Exploration and evaluation expenditure</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/CVB.xlsx
+++ b/output/pdf_financials_xlsx/CVB.xlsx
@@ -950,46 +950,46 @@
         <v>0.502119</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.586494</v>
+        <v>1.809752</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.284521</v>
+        <v>0.602011</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.043124</v>
+        <v>0.081972</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.0187</v>
+        <v>0.054741</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.025438</v>
+        <v>0.06472600000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.075418</v>
+        <v>0.878319</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.566387</v>
+        <v>1.247054</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.684104</v>
+        <v>1.431705</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.622175</v>
+        <v>0.905963</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.6221139999999999</v>
+        <v>1.108008</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.521605</v>
+        <v>0.8659019999999999</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.467178</v>
+        <v>0.684327</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.435937</v>
+        <v>0.758831</v>
       </c>
       <c r="R10" s="3" t="n">
-        <v>0.456579</v>
+        <v>1.584675</v>
       </c>
     </row>
     <row r="11">
@@ -1012,46 +1012,46 @@
         <v>-0.502119</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.586494</v>
+        <v>-1.809752</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.284521</v>
+        <v>-0.602011</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.043124</v>
+        <v>-0.081972</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.0187</v>
+        <v>-0.054741</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.025438</v>
+        <v>-0.06472600000000001</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.075418</v>
+        <v>-0.878319</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.566387</v>
+        <v>-1.247054</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.684104</v>
+        <v>-1.431705</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.622175</v>
+        <v>-0.905963</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.6221139999999999</v>
+        <v>-1.108008</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.521605</v>
+        <v>-0.8659019999999999</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.467178</v>
+        <v>-0.684327</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.435937</v>
+        <v>-0.758831</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>-0.456579</v>
+        <v>-1.584675</v>
       </c>
     </row>
     <row r="12">
@@ -2505,52 +2505,52 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.03693</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.853089</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.103383</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.085701</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.0005419999999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.001838</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.001775</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>5.436302</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.668915</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>5.020296</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>3.846616</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>1.070415</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.338501</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.125901</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.255977</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.333551</v>
       </c>
     </row>
     <row r="35">
@@ -2625,52 +2625,52 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.03693</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.853089</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.103383</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.085701</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.0005419999999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.001838</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.001775</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>5.436302</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.668915</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>5.020296</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>3.846616</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>1.070415</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.338501</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.125901</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.255977</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.333551</v>
       </c>
     </row>
     <row r="37">
@@ -3348,10 +3348,10 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>2.212541</v>
+        <v>0.359452</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.213383</v>
+        <v>0.11</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -3363,34 +3363,34 @@
         <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.003088</v>
+        <v>0.001313</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.437752</v>
+        <v>0.00145</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.670365</v>
+        <v>0.00145</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>5.021746</v>
+        <v>0.00145</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>3.942752</v>
+        <v>0.096136</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.164922</v>
+        <v>0.09450699999999999</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.414083</v>
+        <v>0.075582</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.176194</v>
+        <v>0.050293</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.262494</v>
+        <v>0.006517</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.337039</v>
+        <v>0.003488</v>
       </c>
     </row>
     <row r="49">
@@ -9175,7 +9175,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -17349,7 +17349,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -32512,7 +32512,7 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -34029,7 +34029,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -34966,10 +34966,10 @@
         </is>
       </c>
       <c r="M259" s="5" t="n">
-        <v>-0.878319</v>
+        <v>0.878319</v>
       </c>
       <c r="N259" s="5" t="n">
-        <v>-1.247054</v>
+        <v>1.247054</v>
       </c>
       <c r="O259" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
@@ -38649,7 +38649,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
@@ -38698,10 +38698,10 @@
         </is>
       </c>
       <c r="N296" s="5" t="n">
-        <v>-1.247054</v>
+        <v>1.247054</v>
       </c>
       <c r="O296" s="5" t="n">
-        <v>-1.431705</v>
+        <v>1.431705</v>
       </c>
       <c r="P296" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
@@ -41469,19 +41469,19 @@
         </is>
       </c>
       <c r="I324" s="5" t="n">
-        <v>-0.602011</v>
+        <v>0.602011</v>
       </c>
       <c r="J324" s="5" t="n">
-        <v>-0.081972</v>
+        <v>0.081972</v>
       </c>
       <c r="K324" s="5" t="n">
-        <v>-0.054741</v>
+        <v>0.054741</v>
       </c>
       <c r="L324" s="5" t="n">
-        <v>-0.06472600000000001</v>
+        <v>0.06472600000000001</v>
       </c>
       <c r="M324" s="5" t="n">
-        <v>-0.878319</v>
+        <v>0.878319</v>
       </c>
       <c r="N324" t="inlineStr">
         <is>
@@ -46748,7 +46748,7 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
@@ -46767,10 +46767,10 @@
         </is>
       </c>
       <c r="H377" s="5" t="n">
-        <v>-1.809752</v>
+        <v>1.809752</v>
       </c>
       <c r="I377" s="5" t="n">
-        <v>-0.602011</v>
+        <v>0.602011</v>
       </c>
       <c r="J377" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
@@ -48877,7 +48877,7 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
